--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_69_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_69_IN_Piura.xlsx
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>8.58</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>10.14</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C12" s="31">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>68.53</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>12.75</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1919,11 +1919,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>19.4253</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1944,11 +1944,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>3.6373</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>18.72</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1969,11 +1969,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>15.788</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>81.28</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2148,11 +2148,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>19.428</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2271,6 +2271,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2417,6 +2418,7 @@
       <c r="F13" s="17" t="inlineStr"/>
       <c r="G13" s="17" t="inlineStr"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -2461,6 +2463,7 @@
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="132" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
@@ -2985,11 +2988,11 @@
       </c>
       <c r="B21" s="33">
         <f>SUM(B10:B20)</f>
-        <v/>
+        <v>481.17</v>
       </c>
       <c r="C21" s="23">
         <f>SUM(C10:C20)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
@@ -2999,19 +3002,19 @@
       <c r="E21" s="17" t="inlineStr"/>
       <c r="F21" s="17">
         <f>ROUND(AVERAGE(F10:F20),2)</f>
-        <v/>
+        <v>29.39</v>
       </c>
       <c r="G21" s="22">
         <f>ROUND(AVERAGE(G10:G20),4)</f>
-        <v/>
+        <v>0.5435</v>
       </c>
       <c r="H21" s="23">
         <f>ROUND(AVERAGE(H10:H20),2)</f>
-        <v/>
+        <v>73.58</v>
       </c>
       <c r="I21" s="23">
         <f>ROUND(AVERAGE(I10:I20),2)</f>
-        <v/>
+        <v>32.8</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1">
